--- a/Data/unitary_authority_data.xlsx
+++ b/Data/unitary_authority_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://scotsconnect-my.sharepoint.com/personal/euan_wakefield_gov_scot/Documents/R/RESAS-Agricultural-Statistics-Hub/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{804F3F20-43A3-4563-8B5B-8A0BE0CF2310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19EB750C-601D-4111-9E0B-50D7AFCD26CD}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{804F3F20-43A3-4563-8B5B-8A0BE0CF2310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9586194-A63C-4EF9-893B-07B08E8CABE4}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" firstSheet="1" activeTab="1" xr2:uid="{B086D461-E5E0-4CA5-AF09-B2445CFA5063}"/>
+    <workbookView xWindow="17" yWindow="17" windowWidth="16440" windowHeight="8520" firstSheet="1" activeTab="1" xr2:uid="{B086D461-E5E0-4CA5-AF09-B2445CFA5063}"/>
   </bookViews>
   <sheets>
     <sheet name="unitary_crops_area" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="144">
   <si>
     <t>unitauth</t>
   </si>
@@ -7136,8 +7136,8 @@
       <c r="Z32" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="AA32" s="5">
-        <v>103</v>
+      <c r="AA32" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="AB32" s="5" t="s">
         <v>143</v>
